--- a/드론 제어부.xlsx
+++ b/드론 제어부.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Gimbal-Drone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jweli\Project\Gimbal-CAM-Drone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E6FEE3-BAC4-441B-9D64-442AE93E2B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1ADF53-8EFB-42A3-94B3-A2B2D99216D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1BB17840-856F-4883-AEC3-D8A86AFF3FA0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1BB17840-856F-4883-AEC3-D8A86AFF3FA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Pin map" sheetId="2" r:id="rId1"/>
@@ -161,14 +161,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CAN Transiver</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ESC와 통신 용도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[부품 목록] 2026-04-24</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -331,10 +323,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BMP388</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NEO-M8N</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -706,6 +694,18 @@
   </si>
   <si>
     <t>PE1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCP2562FD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ESC와 통신 용도 (CAN)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ICP-10111</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1019,6 +1019,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1027,6 +1033,60 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1054,67 +1114,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1569,1242 +1569,1320 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E405377-E618-4100-B705-F7C17A92798B}">
   <dimension ref="A1:N49"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
-    <col min="2" max="2" width="10.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10.19921875" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A1" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A2" s="40"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A3" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A3" s="15" t="s">
+      <c r="C3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="G3" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="N3" s="41"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A4" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="B4" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="N3" s="35"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A4" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="N4" s="50"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
+        <v>118</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="N4" s="20"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A5" s="27"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="18"/>
-      <c r="M5" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="N5" s="50"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
+      <c r="M5" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="N5" s="20"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="N6" s="20"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A7" s="27"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="N6" s="50"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A7" s="32"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="N7" s="50"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A8" s="32"/>
+      <c r="G7" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="N7" s="20"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A8" s="27"/>
       <c r="B8" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="N8" s="50"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A9" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>114</v>
+      <c r="G8" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N8" s="20"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A9" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>111</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="49" t="s">
-        <v>116</v>
-      </c>
-      <c r="N9" s="50"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A10" s="32"/>
-      <c r="B10" s="32"/>
+        <v>125</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="N9" s="20"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
       <c r="L10" s="18"/>
-      <c r="M10" s="49" t="s">
-        <v>139</v>
-      </c>
-      <c r="N10" s="50"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A11" s="32"/>
-      <c r="B11" s="32"/>
+      <c r="M10" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="N10" s="20"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="N11" s="50"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A12" s="32"/>
-      <c r="B12" s="32"/>
+        <v>127</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="N11" s="20"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="49" t="s">
-        <v>145</v>
-      </c>
-      <c r="N12" s="50"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A13" s="32"/>
-      <c r="B13" s="33"/>
+      <c r="G12" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="N12" s="20"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A13" s="27"/>
+      <c r="B13" s="25"/>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="N13" s="50"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A14" s="32"/>
+      <c r="G13" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="N13" s="20"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A14" s="27"/>
       <c r="B14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="42" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="49" t="s">
+      <c r="G14" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N14" s="20"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A15" s="27"/>
+      <c r="B15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="N14" s="50"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A15" s="32"/>
-      <c r="B15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="N15" s="50"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A16" s="32"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="N15" s="20"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="44"/>
-      <c r="M16" s="49" t="s">
+      <c r="G16" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="N16" s="50"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A17" s="32"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N16" s="20"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A17" s="27"/>
       <c r="B17" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="47"/>
-      <c r="M17" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="N17" s="50"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A18" s="33"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="N17" s="20"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A18" s="25"/>
       <c r="B18" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="N18" s="50"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A19" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>158</v>
+        <v>56</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="20"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A19" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>155</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="49" t="s">
-        <v>98</v>
-      </c>
-      <c r="N19" s="50"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A20" s="32"/>
-      <c r="B20" s="33"/>
+        <v>59</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="N19" s="20"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A20" s="27"/>
+      <c r="B20" s="25"/>
       <c r="C20" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="N20" s="20"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A21" s="27"/>
+      <c r="B21" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="N20" s="50"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A21" s="32"/>
-      <c r="B21" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="N21" s="20"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A22" s="27"/>
+      <c r="B22" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="49" t="s">
+      <c r="C22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="N21" s="50"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A22" s="32"/>
-      <c r="B22" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="N22" s="20"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A23" s="27"/>
+      <c r="B23" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="N22" s="50"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A23" s="32"/>
-      <c r="B23" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="49" t="s">
-        <v>149</v>
-      </c>
-      <c r="N23" s="50"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A24" s="33"/>
+        <v>56</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="N23" s="20"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A24" s="25"/>
       <c r="B24" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G24" s="39"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="41"/>
-      <c r="M24" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="N24" s="50"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A25" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="31" t="s">
-        <v>85</v>
+        <v>56</v>
+      </c>
+      <c r="G24" s="37"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="N24" s="20"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A25" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>82</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="N25" s="50"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A26" s="32"/>
-      <c r="B26" s="32"/>
+        <v>89</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="N25" s="20"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A26" s="27"/>
+      <c r="B26" s="27"/>
       <c r="C26" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="49" t="s">
-        <v>139</v>
-      </c>
-      <c r="N26" s="50"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A27" s="32"/>
-      <c r="B27" s="32"/>
+        <v>88</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="N26" s="20"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A27" s="27"/>
+      <c r="B27" s="27"/>
       <c r="C27" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="N27" s="20"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A28" s="27"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="21"/>
-      <c r="M27" s="49" t="s">
-        <v>116</v>
-      </c>
-      <c r="N27" s="50"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A28" s="32"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="49" t="s">
-        <v>157</v>
-      </c>
-      <c r="N28" s="50"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A29" s="33"/>
+        <v>152</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="N28" s="20"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A29" s="25"/>
       <c r="B29" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="N29" s="50"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A30" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="B30" s="31" t="s">
-        <v>161</v>
+        <v>153</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="N29" s="20"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A30" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>158</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="49" t="s">
-        <v>98</v>
-      </c>
-      <c r="N30" s="50"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A31" s="32"/>
-      <c r="B31" s="33"/>
+        <v>161</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="23"/>
+      <c r="M30" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="N30" s="20"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A31" s="27"/>
+      <c r="B31" s="25"/>
       <c r="C31" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="N31" s="50"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A32" s="32"/>
+        <v>162</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="N31" s="20"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A32" s="27"/>
       <c r="B32" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="21"/>
-      <c r="M32" s="49" t="s">
-        <v>108</v>
-      </c>
-      <c r="N32" s="50"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A33" s="32"/>
+      <c r="G32" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="23"/>
+      <c r="M32" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="N32" s="20"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A33" s="27"/>
       <c r="B33" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="49" t="s">
-        <v>109</v>
-      </c>
-      <c r="N33" s="50"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A34" s="33"/>
+      <c r="G33" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="23"/>
+      <c r="M33" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="N33" s="20"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A34" s="25"/>
       <c r="B34" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="21"/>
-      <c r="M34" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="N34" s="50"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A35" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="23"/>
+      <c r="M34" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="N34" s="20"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A35" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="31" t="s">
-        <v>161</v>
+      <c r="B35" s="24" t="s">
+        <v>158</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G35" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="21"/>
-      <c r="M35" s="49"/>
-      <c r="N35" s="50"/>
-    </row>
-    <row r="36" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="32"/>
-      <c r="B36" s="33"/>
+        <v>161</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="23"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="20"/>
+    </row>
+    <row r="36" spans="1:14" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="27"/>
+      <c r="B36" s="25"/>
       <c r="C36" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H36" s="17"/>
       <c r="I36" s="17"/>
       <c r="J36" s="17"/>
       <c r="K36" s="17"/>
       <c r="L36" s="18"/>
-      <c r="M36" s="49"/>
-      <c r="N36" s="50"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A37" s="32"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="20"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A37" s="27"/>
       <c r="B37" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
       <c r="J37" s="17"/>
       <c r="K37" s="17"/>
       <c r="L37" s="18"/>
-      <c r="M37" s="49"/>
-      <c r="N37" s="50"/>
-    </row>
-    <row r="38" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="32"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="20"/>
+    </row>
+    <row r="38" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="27"/>
       <c r="B38" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G38" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="23"/>
-      <c r="K38" s="23"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="49"/>
-      <c r="N38" s="50"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A39" s="32"/>
+        <v>56</v>
+      </c>
+      <c r="G38" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="44"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="20"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A39" s="27"/>
       <c r="B39" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G39" s="25"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="26"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="49"/>
-      <c r="N39" s="50"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A40" s="33"/>
+        <v>56</v>
+      </c>
+      <c r="G39" s="45"/>
+      <c r="H39" s="46"/>
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46"/>
+      <c r="L39" s="47"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="20"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A40" s="25"/>
       <c r="B40" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G40" s="28"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="49"/>
-      <c r="N40" s="50"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A41" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="B41" s="31" t="s">
-        <v>151</v>
+        <v>56</v>
+      </c>
+      <c r="G40" s="48"/>
+      <c r="H40" s="49"/>
+      <c r="I40" s="49"/>
+      <c r="J40" s="49"/>
+      <c r="K40" s="49"/>
+      <c r="L40" s="50"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="20"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A41" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="24" t="s">
+        <v>148</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G41" s="19"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="21"/>
-      <c r="M41" s="49"/>
-      <c r="N41" s="50"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A42" s="32"/>
-      <c r="B42" s="33"/>
+        <v>163</v>
+      </c>
+      <c r="G41" s="21"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="23"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="20"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A42" s="27"/>
+      <c r="B42" s="25"/>
       <c r="C42" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G42" s="49"/>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="51"/>
-      <c r="K42" s="51"/>
-      <c r="L42" s="50"/>
-      <c r="M42" s="49"/>
-      <c r="N42" s="50"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A43" s="33"/>
+        <v>164</v>
+      </c>
+      <c r="G42" s="19"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="19"/>
+      <c r="N42" s="20"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A43" s="25"/>
       <c r="B43" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="51"/>
-      <c r="J43" s="51"/>
-      <c r="K43" s="51"/>
-      <c r="L43" s="50"/>
-      <c r="M43" s="49"/>
-      <c r="N43" s="50"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A44" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="B44" s="31" t="s">
-        <v>95</v>
+      <c r="G43" s="19"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+      <c r="K43" s="26"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="20"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A44" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>92</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="49"/>
-      <c r="H44" s="51"/>
-      <c r="I44" s="51"/>
-      <c r="J44" s="51"/>
-      <c r="K44" s="51"/>
-      <c r="L44" s="50"/>
-      <c r="M44" s="49"/>
-      <c r="N44" s="50"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A45" s="33"/>
-      <c r="B45" s="33"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="26"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="20"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A45" s="25"/>
+      <c r="B45" s="25"/>
       <c r="C45" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
-      <c r="G45" s="49"/>
-      <c r="H45" s="51"/>
-      <c r="I45" s="51"/>
-      <c r="J45" s="51"/>
-      <c r="K45" s="51"/>
-      <c r="L45" s="50"/>
-      <c r="M45" s="49"/>
-      <c r="N45" s="50"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="G45" s="19"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="20"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
-      <c r="G46" s="49"/>
-      <c r="H46" s="51"/>
-      <c r="I46" s="51"/>
-      <c r="J46" s="51"/>
-      <c r="K46" s="51"/>
-      <c r="L46" s="50"/>
-      <c r="M46" s="49"/>
-      <c r="N46" s="50"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="G46" s="19"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="26"/>
+      <c r="K46" s="26"/>
+      <c r="L46" s="20"/>
+      <c r="M46" s="19"/>
+      <c r="N46" s="20"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
-      <c r="G47" s="49"/>
-      <c r="H47" s="51"/>
-      <c r="I47" s="51"/>
-      <c r="J47" s="51"/>
-      <c r="K47" s="51"/>
-      <c r="L47" s="50"/>
-      <c r="M47" s="49"/>
-      <c r="N47" s="50"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="G47" s="19"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="26"/>
+      <c r="K47" s="26"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="19"/>
+      <c r="N47" s="20"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
-      <c r="G48" s="49"/>
-      <c r="H48" s="51"/>
-      <c r="I48" s="51"/>
-      <c r="J48" s="51"/>
-      <c r="K48" s="51"/>
-      <c r="L48" s="50"/>
-      <c r="M48" s="49"/>
-      <c r="N48" s="50"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="G48" s="19"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="26"/>
+      <c r="K48" s="26"/>
+      <c r="L48" s="20"/>
+      <c r="M48" s="19"/>
+      <c r="N48" s="20"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
-      <c r="G49" s="49"/>
-      <c r="H49" s="51"/>
-      <c r="I49" s="51"/>
-      <c r="J49" s="51"/>
-      <c r="K49" s="51"/>
-      <c r="L49" s="50"/>
-      <c r="M49" s="49"/>
-      <c r="N49" s="50"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="26"/>
+      <c r="K49" s="26"/>
+      <c r="L49" s="20"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="102">
+    <mergeCell ref="G48:L48"/>
+    <mergeCell ref="G49:L49"/>
+    <mergeCell ref="G38:L40"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="G47:L47"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="A25:A29"/>
+    <mergeCell ref="A1:N2"/>
+    <mergeCell ref="G3:L3"/>
+    <mergeCell ref="G4:L4"/>
+    <mergeCell ref="G7:L7"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="A9:A18"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="G13:L13"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="A19:A24"/>
+    <mergeCell ref="G23:L24"/>
+    <mergeCell ref="G29:L29"/>
+    <mergeCell ref="G25:L25"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="G27:L27"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="G19:L19"/>
+    <mergeCell ref="G20:L20"/>
+    <mergeCell ref="G21:L21"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="G35:L35"/>
+    <mergeCell ref="G34:L34"/>
+    <mergeCell ref="G31:L31"/>
+    <mergeCell ref="G32:L32"/>
+    <mergeCell ref="G33:L33"/>
+    <mergeCell ref="B9:B13"/>
+    <mergeCell ref="G16:L17"/>
+    <mergeCell ref="G14:L15"/>
+    <mergeCell ref="G30:L30"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M27:N27"/>
     <mergeCell ref="M48:N48"/>
     <mergeCell ref="M49:N49"/>
     <mergeCell ref="G12:L12"/>
@@ -2829,84 +2907,6 @@
     <mergeCell ref="M42:N42"/>
     <mergeCell ref="M33:N33"/>
     <mergeCell ref="M34:N34"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="G35:L35"/>
-    <mergeCell ref="G34:L34"/>
-    <mergeCell ref="G31:L31"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="B9:B13"/>
-    <mergeCell ref="G16:L17"/>
-    <mergeCell ref="G14:L15"/>
-    <mergeCell ref="A9:A18"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="G13:L13"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="A19:A24"/>
-    <mergeCell ref="G23:L24"/>
-    <mergeCell ref="G29:L29"/>
-    <mergeCell ref="G30:L30"/>
-    <mergeCell ref="G25:L25"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="G27:L27"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="G19:L19"/>
-    <mergeCell ref="G20:L20"/>
-    <mergeCell ref="G21:L21"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="A25:A29"/>
-    <mergeCell ref="A1:N2"/>
-    <mergeCell ref="G3:L3"/>
-    <mergeCell ref="G4:L4"/>
-    <mergeCell ref="G7:L7"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="G48:L48"/>
-    <mergeCell ref="G49:L49"/>
-    <mergeCell ref="G38:L40"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="G47:L47"/>
-    <mergeCell ref="A44:A45"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2917,54 +2917,54 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36D134F5-4780-4C74-8E01-5290E7893904}">
   <dimension ref="A1:N34"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.9140625" customWidth="1"/>
+    <col min="1" max="1" width="15.296875" customWidth="1"/>
+    <col min="2" max="2" width="21.8984375" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.796875" customWidth="1"/>
+    <col min="7" max="7" width="11.796875" customWidth="1"/>
     <col min="8" max="8" width="34" customWidth="1"/>
-    <col min="12" max="12" width="11.08203125" customWidth="1"/>
+    <col min="12" max="12" width="11.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A1" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A1" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A2" s="40"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -3018,11 +3018,11 @@
         <v>12</v>
       </c>
       <c r="J4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A5" s="48" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A5" s="51" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -3049,8 +3049,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A6" s="48"/>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A6" s="51"/>
       <c r="B6" s="3" t="s">
         <v>14</v>
       </c>
@@ -3076,12 +3076,12 @@
       </c>
       <c r="L6" s="13"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>8</v>
@@ -3101,15 +3101,15 @@
         <v>3.9599999999999991E-3</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>8</v>
@@ -3129,14 +3129,14 @@
         <v>2.64E-3</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>541.03</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="10" t="s">
@@ -3195,10 +3195,10 @@
       </c>
       <c r="L10" s="14">
         <f>SUMIF(D:D, 5, E:E)</f>
-        <v>151.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+        <v>221.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -3226,12 +3226,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>8</v>
@@ -3251,11 +3251,11 @@
         <v>0.75</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A13" s="31" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A13" s="24" t="s">
         <v>29</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -3279,11 +3279,11 @@
         <v>0.495</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A14" s="32"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A14" s="27"/>
       <c r="B14" s="3"/>
       <c r="C14" s="10"/>
       <c r="D14" s="5"/>
@@ -3297,32 +3297,36 @@
         <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A15" s="33"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A15" s="25"/>
       <c r="B15" s="3" t="s">
-        <v>31</v>
+        <v>165</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="7"/>
+      <c r="D15" s="5">
+        <v>5</v>
+      </c>
+      <c r="E15" s="7">
+        <v>70</v>
+      </c>
       <c r="F15" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="G15" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="10"/>
@@ -3338,7 +3342,7 @@
       </c>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="10"/>
@@ -3354,7 +3358,7 @@
       </c>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="10"/>
@@ -3370,7 +3374,7 @@
       </c>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="10"/>
@@ -3386,7 +3390,7 @@
       </c>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="10"/>
@@ -3402,7 +3406,7 @@
       </c>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="10"/>
@@ -3418,7 +3422,7 @@
       </c>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="10"/>
@@ -3434,7 +3438,7 @@
       </c>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="10"/>
@@ -3450,7 +3454,7 @@
       </c>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="10"/>
@@ -3466,7 +3470,7 @@
       </c>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="10"/>
@@ -3482,7 +3486,7 @@
       </c>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="10"/>
@@ -3498,7 +3502,7 @@
       </c>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="10"/>
@@ -3514,7 +3518,7 @@
       </c>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="10"/>
@@ -3530,7 +3534,7 @@
       </c>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="10"/>
@@ -3546,7 +3550,7 @@
       </c>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="10"/>
@@ -3562,7 +3566,7 @@
       </c>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="11"/>
@@ -3578,7 +3582,7 @@
       </c>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="11"/>
@@ -3594,7 +3598,7 @@
       </c>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="11"/>
@@ -3610,7 +3614,7 @@
       </c>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="11"/>
